--- a/etl/data/inputs/Dr Verweys Tank Cleaning Guide Oil - procedure template steps.xlsx
+++ b/etl/data/inputs/Dr Verweys Tank Cleaning Guide Oil - procedure template steps.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="54">
   <si>
     <t xml:space="preserve">procedure_code</t>
   </si>
@@ -191,7 +191,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -228,12 +228,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
     <font>
       <b val="true"/>
@@ -299,7 +293,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -312,19 +306,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -406,7 +396,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N1048576"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="33.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.88"/>
@@ -879,7 +869,7 @@
       <c r="D16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>34</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -999,7 +989,7 @@
       <c r="D20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>38</v>
       </c>
       <c r="F20" s="2" t="s">
@@ -1773,33 +1763,36 @@
       <c r="N46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="5" t="s">
+      <c r="B47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="5" t="s">
         <v>38</v>
       </c>
       <c r="F47" s="0" t="s">
         <v>15</v>
       </c>
+      <c r="H47" s="0" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="2" t="s">
@@ -1819,10 +1812,10 @@
       <c r="A49" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
@@ -1839,10 +1832,10 @@
       <c r="A50" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D50" s="2" t="s">
@@ -1853,13 +1846,13 @@
       <c r="A51" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="4" t="s">
         <v>13</v>
       </c>
     </row>
